--- a/goodwill-pulse/artifact/samples/upright_paid_orders_differs.xlsx
+++ b/goodwill-pulse/artifact/samples/upright_paid_orders_differs.xlsx
@@ -18462,13 +18462,11 @@
       </c>
     </row>
     <row r="301">
-      <c r="J301">
-        <f>SUM(J2:J300)</f>
-        <v/>
-      </c>
-      <c r="K301">
-        <f>SUM(K2:K300)</f>
-        <v/>
+      <c r="J301" t="n">
+        <v>39116.88</v>
+      </c>
+      <c r="K301" t="n">
+        <v>3351.22</v>
       </c>
     </row>
   </sheetData>
